--- a/Content/kr_estimate_A.xlsx
+++ b/Content/kr_estimate_A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22325"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YSN2017\Content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB2F577-A3EA-4574-8699-0533A30028DE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B871BE1A-2DB8-4EAF-AA6B-E6554D71DC0A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="9" r:id="rId1"/>
@@ -23,7 +23,9 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -51,9 +53,6 @@
   <si>
     <t xml:space="preserve"> </t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>세부견적내역</t>
@@ -99,10 +98,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>총합계금액</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>비   고</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -120,10 +115,6 @@
   </si>
   <si>
     <t>1. 위 제품에 대한 내용물과의 적합성 여부는 테스트를 통해 필히 검증(고객사)하여야 함</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>재질</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -223,19 +214,30 @@
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>총합계금액(원)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>구분</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>수량</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="#,##0_ "/>
     <numFmt numFmtId="178" formatCode="#,##0\ &quot;EA&quot;"/>
     <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="180" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="181" formatCode="#,##0_);[Red]\(#,##0\)"/>
+    <numFmt numFmtId="180" formatCode="#,##0_);\(#,##0\)"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -341,7 +343,8 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <u/>
+      <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="돋움"/>
       <family val="3"/>
@@ -351,22 +354,20 @@
       <b/>
       <u/>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
-      <b/>
-      <u/>
-      <sz val="12"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="돋움"/>
       <family val="3"/>
@@ -387,7 +388,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="47">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -672,19 +673,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="hair">
         <color indexed="64"/>
       </left>
@@ -768,48 +756,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -922,11 +868,103 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="hair">
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -941,7 +979,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1027,110 +1065,164 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="9" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="16" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="16" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1139,22 +1231,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1166,7 +1249,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1175,151 +1258,31 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="16" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="16" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="16" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1961,6 +1924,80 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>15610</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>236373</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>404208</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>78574</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 1" descr="원-직인">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C372669A-AE18-49F2-916B-35BD0D2BCD09}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="email">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5107822" y="1621161"/>
+          <a:ext cx="388598" cy="399048"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2291,13 +2328,13 @@
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="22.375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="5.375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="4.75" style="4" customWidth="1"/>
-    <col min="5" max="5" width="6.875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="5.5" style="4" customWidth="1"/>
-    <col min="7" max="7" width="4.375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9.375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="17.375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="0.875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8" style="4" customWidth="1"/>
+    <col min="5" max="5" width="4.375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="4.125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6" style="4" customWidth="1"/>
     <col min="8" max="8" width="5.125" style="4" customWidth="1"/>
     <col min="9" max="10" width="8.625" style="4" customWidth="1"/>
     <col min="11" max="11" width="8.5" style="4" customWidth="1"/>
@@ -3000,15 +3037,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
       <c r="H1" s="1"/>
       <c r="I1" s="2" t="s">
         <v>1</v>
@@ -3021,15 +3058,15 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="59"/>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="65"/>
+      <c r="I2" s="83"/>
       <c r="J2" s="6" t="s">
         <v>4</v>
       </c>
@@ -3038,19 +3075,19 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="68" t="s">
-        <v>29</v>
+      <c r="A3" s="102" t="s">
+        <v>26</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68" t="s">
-        <v>30</v>
+      <c r="B3" s="102"/>
+      <c r="C3" s="95" t="s">
+        <v>27</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="69"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="96"/>
       <c r="H3" s="5"/>
-      <c r="I3" s="66"/>
+      <c r="I3" s="84"/>
       <c r="J3" s="9" t="s">
         <v>4</v>
       </c>
@@ -3072,18 +3109,18 @@
       <c r="K4" s="16"/>
     </row>
     <row r="5" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="124" t="s">
-        <v>28</v>
+      <c r="A5" s="85" t="s">
+        <v>25</v>
       </c>
-      <c r="B5" s="67"/>
+      <c r="B5" s="86"/>
       <c r="C5" s="17"/>
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
       <c r="F5" s="18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H5" s="20"/>
       <c r="I5" s="17"/>
@@ -3091,16 +3128,16 @@
       <c r="K5" s="21"/>
     </row>
     <row r="6" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="77" t="s">
-        <v>26</v>
+      <c r="A6" s="92" t="s">
+        <v>23</v>
       </c>
-      <c r="B6" s="78"/>
+      <c r="B6" s="93"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="18"/>
       <c r="G6" s="19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H6" s="20"/>
       <c r="I6" s="17"/>
@@ -3108,18 +3145,18 @@
       <c r="K6" s="21"/>
     </row>
     <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="74" t="s">
-        <v>27</v>
+      <c r="A7" s="89" t="s">
+        <v>24</v>
       </c>
-      <c r="B7" s="75"/>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="76"/>
+      <c r="B7" s="90"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="91"/>
       <c r="F7" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H7" s="20"/>
       <c r="I7" s="17"/>
@@ -3129,14 +3166,14 @@
     <row r="8" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="22"/>
       <c r="B8" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
       <c r="G8" s="19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H8" s="20"/>
       <c r="I8" s="17"/>
@@ -3145,17 +3182,17 @@
     </row>
     <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H9" s="20"/>
       <c r="I9" s="17"/>
@@ -3176,456 +3213,388 @@
       <c r="K10" s="28"/>
     </row>
     <row r="11" spans="1:14" ht="22.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="70" t="s">
-        <v>17</v>
+      <c r="A11" s="87" t="s">
+        <v>28</v>
       </c>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="88"/>
     </row>
     <row r="12" spans="1:14" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="60" t="s">
-        <v>6</v>
+      <c r="C12" s="79"/>
+      <c r="D12" s="80" t="s">
+        <v>30</v>
       </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="62" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="63"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="62" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="63"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="62" t="s">
+      <c r="E12" s="81"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="K12" s="79"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="80" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="94"/>
     </row>
     <row r="13" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="29"/>
-      <c r="B13" s="92"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="89"/>
-      <c r="H13" s="90"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="80"/>
-      <c r="K13" s="81"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="66"/>
+      <c r="K13" s="67"/>
     </row>
     <row r="14" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="29"/>
-      <c r="B14" s="87"/>
-      <c r="C14" s="88"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="82"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="84"/>
-      <c r="J14" s="85"/>
-      <c r="K14" s="86"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="31"/>
     </row>
     <row r="15" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="29"/>
-      <c r="B15" s="92"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="97"/>
-      <c r="H15" s="98"/>
-      <c r="I15" s="99"/>
-      <c r="J15" s="85"/>
-      <c r="K15" s="86"/>
-      <c r="L15" s="33"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="31"/>
     </row>
     <row r="16" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="31"/>
-      <c r="B16" s="92"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="94"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="52"/>
-      <c r="K16" s="53"/>
-      <c r="N16" s="33"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="76"/>
+      <c r="N16" s="31"/>
     </row>
     <row r="17" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="125"/>
-      <c r="B17" s="126"/>
-      <c r="C17" s="126"/>
-      <c r="D17" s="126"/>
-      <c r="E17" s="126"/>
-      <c r="F17" s="126"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="45"/>
-      <c r="M17" s="33"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="38"/>
+      <c r="M17" s="31"/>
     </row>
     <row r="18" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="31"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="41"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="101"/>
     </row>
     <row r="19" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="125"/>
-      <c r="B19" s="126"/>
-      <c r="C19" s="126"/>
-      <c r="D19" s="126"/>
-      <c r="E19" s="126"/>
-      <c r="F19" s="126"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="45"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="38"/>
     </row>
     <row r="20" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="31"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="94"/>
-      <c r="H20" s="95"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="41"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="100"/>
+      <c r="K20" s="101"/>
     </row>
     <row r="21" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="125"/>
-      <c r="B21" s="126"/>
-      <c r="C21" s="126"/>
-      <c r="D21" s="126"/>
-      <c r="E21" s="126"/>
-      <c r="F21" s="126"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="45"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="38"/>
       <c r="M21" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="31"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="52"/>
-      <c r="K22" s="53"/>
+      <c r="A22" s="34"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="75"/>
+      <c r="K22" s="76"/>
     </row>
     <row r="23" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="31"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="52"/>
-      <c r="K23" s="53"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="75"/>
+      <c r="K23" s="76"/>
     </row>
     <row r="24" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="31"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="57"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="52"/>
-      <c r="K24" s="53"/>
+      <c r="A24" s="34"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="76"/>
     </row>
     <row r="25" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="127"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="44"/>
-      <c r="K25" s="45"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="38"/>
     </row>
     <row r="26" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="31"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="52"/>
-      <c r="K26" s="53"/>
+      <c r="A26" s="34"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="75"/>
+      <c r="K26" s="76"/>
     </row>
     <row r="27" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="127"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="44"/>
-      <c r="K27" s="45"/>
+      <c r="A27" s="35"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="38"/>
     </row>
     <row r="28" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="31"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="52"/>
-      <c r="K28" s="53"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="75"/>
+      <c r="K28" s="76"/>
     </row>
     <row r="29" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="31"/>
-      <c r="B29" s="122"/>
-      <c r="C29" s="123"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="54"/>
-      <c r="K29" s="55"/>
+      <c r="A29" s="34"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="97"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="99"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="73"/>
+      <c r="K29" s="74"/>
     </row>
     <row r="30" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="127"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44"/>
-      <c r="K30" s="45"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="38"/>
     </row>
     <row r="31" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="29"/>
-      <c r="B31" s="118"/>
-      <c r="C31" s="119"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="108"/>
-      <c r="H31" s="109"/>
-      <c r="I31" s="110"/>
-      <c r="J31" s="100"/>
-      <c r="K31" s="101"/>
+      <c r="A31" s="33"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="44"/>
     </row>
     <row r="32" spans="1:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="29"/>
-      <c r="B32" s="118"/>
-      <c r="C32" s="119"/>
-      <c r="D32" s="105"/>
-      <c r="E32" s="106"/>
-      <c r="F32" s="107"/>
-      <c r="G32" s="108"/>
-      <c r="H32" s="109"/>
-      <c r="I32" s="110"/>
-      <c r="J32" s="100"/>
-      <c r="K32" s="101"/>
+      <c r="A32" s="36"/>
+      <c r="B32" s="65"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="49"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="51"/>
     </row>
     <row r="33" spans="1:11" ht="19.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="30"/>
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="72"/>
-      <c r="H33" s="72"/>
-      <c r="I33" s="72"/>
-      <c r="J33" s="71" t="s">
-        <v>7</v>
+      <c r="A33" s="29"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="52" t="s">
+        <v>6</v>
       </c>
-      <c r="K33" s="111"/>
+      <c r="K33" s="57"/>
     </row>
     <row r="34" spans="1:11" ht="19.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="112" t="s">
+      <c r="A34" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="59"/>
+      <c r="C34" s="59"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="59"/>
+      <c r="I34" s="59"/>
+      <c r="J34" s="59"/>
+      <c r="K34" s="60"/>
+    </row>
+    <row r="35" spans="1:11" ht="19.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="61" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" s="62"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="62"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="62"/>
+      <c r="I35" s="62"/>
+      <c r="J35" s="62"/>
+      <c r="K35" s="63"/>
+    </row>
+    <row r="36" spans="1:11" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="113"/>
-      <c r="C34" s="113"/>
-      <c r="D34" s="113"/>
-      <c r="E34" s="113"/>
-      <c r="F34" s="113"/>
-      <c r="G34" s="113"/>
-      <c r="H34" s="113"/>
-      <c r="I34" s="113"/>
-      <c r="J34" s="113"/>
-      <c r="K34" s="114"/>
-    </row>
-    <row r="35" spans="1:11" ht="19.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="115" t="s">
-        <v>24</v>
-      </c>
-      <c r="B35" s="116"/>
-      <c r="C35" s="116"/>
-      <c r="D35" s="116"/>
-      <c r="E35" s="116"/>
-      <c r="F35" s="116"/>
-      <c r="G35" s="116"/>
-      <c r="H35" s="116"/>
-      <c r="I35" s="116"/>
-      <c r="J35" s="116"/>
-      <c r="K35" s="117"/>
-    </row>
-    <row r="36" spans="1:11" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="102" t="s">
-        <v>25</v>
-      </c>
-      <c r="B36" s="103"/>
-      <c r="C36" s="103"/>
-      <c r="D36" s="103"/>
-      <c r="E36" s="103"/>
-      <c r="F36" s="103"/>
-      <c r="G36" s="103"/>
-      <c r="H36" s="103"/>
-      <c r="I36" s="103"/>
-      <c r="J36" s="103"/>
-      <c r="K36" s="104"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
+      <c r="J36" s="46"/>
+      <c r="K36" s="47"/>
     </row>
     <row r="37" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" s="121"/>
-      <c r="B40" s="121"/>
-      <c r="C40" s="120"/>
-      <c r="D40" s="120"/>
-      <c r="E40" s="120"/>
+      <c r="A40" s="40"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
     </row>
   </sheetData>
-  <mergeCells count="94">
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A35:K35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:K11"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="B22:C22"/>
+  <mergeCells count="101">
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="D29:F29"/>
     <mergeCell ref="J22:K22"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="D22:F22"/>
+    <mergeCell ref="J25:K25"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="G22:I22"/>
@@ -3639,12 +3608,87 @@
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="G18:I18"/>
     <mergeCell ref="G20:I20"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="D19:F19"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="D21:F21"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:K11"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A35:K35"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Content/kr_estimate_A.xlsx
+++ b/Content/kr_estimate_A.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YSN2017\Content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B871BE1A-2DB8-4EAF-AA6B-E6554D71DC0A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A347EAE-A3BE-4132-9443-980EBA64FFE5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34140" yWindow="1935" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="9" r:id="rId1"/>
@@ -233,9 +233,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="#,##0_ "/>
-    <numFmt numFmtId="178" formatCode="#,##0\ &quot;EA&quot;"/>
     <numFmt numFmtId="179" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="180" formatCode="#,##0_);\(#,##0\)"/>
   </numFmts>
@@ -970,7 +970,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -978,8 +978,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1087,22 +1090,142 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="16" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1120,9 +1243,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="180" fontId="16" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1130,24 +1250,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="16" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1168,125 +1270,30 @@
     <xf numFmtId="4" fontId="7" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="41" fontId="16" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="2" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="2" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="2" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="쉼표 [0]" xfId="3" builtinId="6"/>
     <cellStyle name="통화 [0]" xfId="1" builtinId="7"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -3037,15 +3044,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="1"/>
       <c r="I1" s="2" t="s">
         <v>1</v>
@@ -3058,15 +3065,15 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="83"/>
+      <c r="I2" s="53"/>
       <c r="J2" s="6" t="s">
         <v>4</v>
       </c>
@@ -3075,19 +3082,19 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="102" t="s">
+      <c r="A3" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="102"/>
-      <c r="C3" s="95" t="s">
+      <c r="B3" s="37"/>
+      <c r="C3" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="96"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="68"/>
       <c r="H3" s="5"/>
-      <c r="I3" s="84"/>
+      <c r="I3" s="54"/>
       <c r="J3" s="9" t="s">
         <v>4</v>
       </c>
@@ -3109,10 +3116,10 @@
       <c r="K4" s="16"/>
     </row>
     <row r="5" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="86"/>
+      <c r="B5" s="56"/>
       <c r="C5" s="17"/>
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
@@ -3128,10 +3135,10 @@
       <c r="K5" s="21"/>
     </row>
     <row r="6" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="93"/>
+      <c r="B6" s="65"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
@@ -3145,13 +3152,13 @@
       <c r="K6" s="21"/>
     </row>
     <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="89" t="s">
+      <c r="A7" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="90"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="91"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="63"/>
       <c r="F7" s="18" t="s">
         <v>10</v>
       </c>
@@ -3213,381 +3220,458 @@
       <c r="K10" s="28"/>
     </row>
     <row r="11" spans="1:14" ht="22.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="87" t="s">
+      <c r="A11" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="88"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="60"/>
     </row>
     <row r="12" spans="1:14" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A12" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="78" t="s">
+      <c r="B12" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="79"/>
-      <c r="D12" s="80" t="s">
+      <c r="C12" s="49"/>
+      <c r="D12" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="81"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="80" t="s">
+      <c r="E12" s="51"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="81"/>
-      <c r="I12" s="82"/>
-      <c r="J12" s="80" t="s">
+      <c r="H12" s="51"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="94"/>
+      <c r="K12" s="66"/>
     </row>
     <row r="13" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="32"/>
-      <c r="B13" s="72"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="66"/>
-      <c r="K13" s="67"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="97"/>
+      <c r="F13" s="97"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
     </row>
     <row r="14" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="33"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="68"/>
-      <c r="K14" s="69"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="74"/>
       <c r="L14" s="31"/>
       <c r="M14" s="31"/>
     </row>
     <row r="15" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="33"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="69"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="98"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="74"/>
       <c r="L15" s="31"/>
     </row>
     <row r="16" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="34"/>
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="75"/>
-      <c r="K16" s="76"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="98"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="98"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="41"/>
       <c r="N16" s="31"/>
     </row>
     <row r="17" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="35"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="38"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="43"/>
       <c r="M17" s="31"/>
     </row>
     <row r="18" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="34"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="97"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="101"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="101"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="39"/>
     </row>
     <row r="19" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="35"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="38"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="43"/>
     </row>
     <row r="20" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="34"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="97"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="99"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="100"/>
-      <c r="K20" s="101"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="101"/>
+      <c r="F20" s="102"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="39"/>
     </row>
     <row r="21" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="35"/>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="38"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="43"/>
       <c r="M21" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="34"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="76"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="98"/>
+      <c r="E22" s="98"/>
+      <c r="F22" s="98"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="41"/>
     </row>
     <row r="23" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34"/>
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="75"/>
-      <c r="K23" s="76"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="98"/>
+      <c r="E23" s="98"/>
+      <c r="F23" s="98"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="41"/>
     </row>
     <row r="24" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="34"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="75"/>
-      <c r="K24" s="76"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="41"/>
     </row>
     <row r="25" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="35"/>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="38"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="99"/>
+      <c r="E25" s="99"/>
+      <c r="F25" s="99"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="43"/>
     </row>
     <row r="26" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="34"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="75"/>
-      <c r="K26" s="76"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="98"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="98"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="41"/>
     </row>
     <row r="27" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="35"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="38"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="99"/>
+      <c r="E27" s="99"/>
+      <c r="F27" s="99"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="43"/>
     </row>
     <row r="28" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="34"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="75"/>
-      <c r="K28" s="76"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="98"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="98"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="41"/>
     </row>
     <row r="29" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="34"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="54"/>
-      <c r="D29" s="97"/>
-      <c r="E29" s="98"/>
-      <c r="F29" s="99"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="73"/>
-      <c r="K29" s="74"/>
+      <c r="B29" s="75"/>
+      <c r="C29" s="75"/>
+      <c r="D29" s="100"/>
+      <c r="E29" s="101"/>
+      <c r="F29" s="102"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="69"/>
+      <c r="K29" s="70"/>
     </row>
     <row r="30" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="35"/>
-      <c r="B30" s="37"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="37"/>
-      <c r="K30" s="38"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="99"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="99"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="43"/>
     </row>
     <row r="31" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33"/>
-      <c r="B31" s="64"/>
-      <c r="C31" s="64"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="42"/>
-      <c r="J31" s="43"/>
-      <c r="K31" s="44"/>
+      <c r="B31" s="79"/>
+      <c r="C31" s="79"/>
+      <c r="D31" s="98"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="98"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="83"/>
+      <c r="K31" s="84"/>
     </row>
     <row r="32" spans="1:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="36"/>
-      <c r="B32" s="65"/>
-      <c r="C32" s="65"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="50"/>
-      <c r="K32" s="51"/>
+      <c r="B32" s="80"/>
+      <c r="C32" s="80"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="103"/>
+      <c r="F32" s="103"/>
+      <c r="G32" s="88"/>
+      <c r="H32" s="88"/>
+      <c r="I32" s="88"/>
+      <c r="J32" s="89"/>
+      <c r="K32" s="90"/>
     </row>
     <row r="33" spans="1:11" ht="19.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="29"/>
-      <c r="B33" s="52"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="53"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="52" t="s">
+      <c r="B33" s="58"/>
+      <c r="C33" s="58"/>
+      <c r="D33" s="58"/>
+      <c r="E33" s="58"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="59"/>
+      <c r="H33" s="59"/>
+      <c r="I33" s="59"/>
+      <c r="J33" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="K33" s="57"/>
+      <c r="K33" s="78"/>
     </row>
     <row r="34" spans="1:11" ht="19.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="58" t="s">
+      <c r="A34" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="B34" s="59"/>
-      <c r="C34" s="59"/>
-      <c r="D34" s="59"/>
-      <c r="E34" s="59"/>
-      <c r="F34" s="59"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="59"/>
-      <c r="I34" s="59"/>
-      <c r="J34" s="59"/>
-      <c r="K34" s="60"/>
+      <c r="B34" s="92"/>
+      <c r="C34" s="92"/>
+      <c r="D34" s="92"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="92"/>
+      <c r="G34" s="92"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="92"/>
+      <c r="J34" s="92"/>
+      <c r="K34" s="93"/>
     </row>
     <row r="35" spans="1:11" ht="19.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="61" t="s">
+      <c r="A35" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="62"/>
-      <c r="C35" s="62"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
-      <c r="I35" s="62"/>
-      <c r="J35" s="62"/>
-      <c r="K35" s="63"/>
+      <c r="B35" s="95"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="95"/>
+      <c r="E35" s="95"/>
+      <c r="F35" s="95"/>
+      <c r="G35" s="95"/>
+      <c r="H35" s="95"/>
+      <c r="I35" s="95"/>
+      <c r="J35" s="95"/>
+      <c r="K35" s="96"/>
     </row>
     <row r="36" spans="1:11" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
-      <c r="K36" s="47"/>
+      <c r="B36" s="86"/>
+      <c r="C36" s="86"/>
+      <c r="D36" s="86"/>
+      <c r="E36" s="86"/>
+      <c r="F36" s="86"/>
+      <c r="G36" s="86"/>
+      <c r="H36" s="86"/>
+      <c r="I36" s="86"/>
+      <c r="J36" s="86"/>
+      <c r="K36" s="87"/>
     </row>
     <row r="37" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" s="40"/>
-      <c r="B40" s="40"/>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="39"/>
+      <c r="A40" s="82"/>
+      <c r="B40" s="82"/>
+      <c r="C40" s="81"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="101">
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:K11"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D20:F20"/>
     <mergeCell ref="J18:K18"/>
     <mergeCell ref="J20:K20"/>
     <mergeCell ref="D29:F29"/>
@@ -3612,83 +3696,6 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:K11"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A35:K35"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
